--- a/Java基礎①_変数_演習問題.xlsx
+++ b/Java基礎①_変数_演習問題.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\片村 涼乃\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pleiades-2024-12-java-win-64bit-jre_20250120~\workspace\Java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E915ECD-3261-4FDC-8D2A-FC71E987EEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D4A44C-75B2-4508-B09F-645F29D3C948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10350" yWindow="-15375" windowWidth="17280" windowHeight="14010" xr2:uid="{D2EB637F-B022-47FB-AE76-97F394918620}"/>
+    <workbookView xWindow="11544" yWindow="0" windowWidth="11592" windowHeight="13056" activeTab="1" xr2:uid="{D2EB637F-B022-47FB-AE76-97F394918620}"/>
   </bookViews>
   <sheets>
     <sheet name="第1章 Javaプログラミングの基礎" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="126">
   <si>
     <t>第1章：Javaプログラミングの基礎</t>
     <phoneticPr fontId="2"/>
@@ -382,9 +382,6 @@
   </si>
   <si>
     <t xml:space="preserve">        double y = 2.0;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        double z = Math.pow(x, y) - Math.sqrt(y);</t>
   </si>
   <si>
     <t xml:space="preserve">        System.out.println((int)z);</t>
@@ -444,18 +441,6 @@
     <t>以下のコードの出力結果を答えてください。</t>
   </si>
   <si>
-    <t>int x = 5;</t>
-  </si>
-  <si>
-    <t>x++;</t>
-  </si>
-  <si>
-    <t>x--;</t>
-  </si>
-  <si>
-    <t>System.out.println(x);</t>
-  </si>
-  <si>
     <t>問12.</t>
     <rPh sb="0" eb="1">
       <t>トイ</t>
@@ -463,15 +448,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>次のうち、コンパイルエラーになる行を選びなさい。</t>
-  </si>
-  <si>
-    <t>final int MAX = 100;</t>
-  </si>
-  <si>
-    <t>MAX = 200;</t>
-  </si>
-  <si>
     <t>System.out.println(MAX);</t>
   </si>
   <si>
@@ -479,9 +455,6 @@
   </si>
   <si>
     <t>B. MAX = 200;</t>
-  </si>
-  <si>
-    <t>C. System.out.println(MAX);</t>
   </si>
   <si>
     <t>問13.</t>
@@ -491,15 +464,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>double d = 9.7;</t>
-  </si>
-  <si>
-    <t>int i = (int) d;</t>
-  </si>
-  <si>
-    <t>System.out.println(i);</t>
-  </si>
-  <si>
     <t>問14.</t>
     <rPh sb="0" eb="1">
       <t>トイ</t>
@@ -507,14 +471,8 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>次のコードはコンパイルエラーになりますか。</t>
-  </si>
-  <si>
     <t>理由と併せて○か×で答えてください。</t>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>int x;</t>
   </si>
   <si>
     <t>１（.javaを書く（人間）
@@ -579,6 +537,84 @@
   </si>
   <si>
     <t>javacは.javaファイルをコンパイルするコマンドでjavaは.classを実行するコマンド</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>B,D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">        double z = Math.pow(x, y) - Math.sqrt(y);</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>int x = 5;</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>x++;</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>x--;</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>System.out.println(x);</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>次のうち、コンパイルエラーになる行を選びなさい。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>final int MAX = 100;</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MAX = 200;</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C. System.out.println(MAX);</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>double d = 9.7;</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>int i = (int) d;</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>System.out.println(i);</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>次のコードはコンパイルエラーになりますか。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>int x;</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>○</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ｘに値が入っていないから</t>
+    <rPh sb="2" eb="3">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ハイ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1045,7 +1081,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
@@ -1058,11 +1094,11 @@
     </row>
     <row r="10" spans="1:11" ht="84.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="4" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="I10" s="3"/>
       <c r="K10" s="3" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.45">
@@ -1075,7 +1111,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="C13" s="4" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.45">
@@ -1111,7 +1147,7 @@
         <v>16</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
@@ -1232,7 +1268,7 @@
         <v>39</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.45">
@@ -1240,7 +1276,7 @@
         <v>40</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.45">
@@ -1248,7 +1284,7 @@
         <v>41</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1259,7 +1295,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F23503-494B-4FE6-85E2-0289A1187C5D}">
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.19921875" style="2" customWidth="1"/>
@@ -1414,7 +1450,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
         <v>69</v>
       </c>
@@ -1422,17 +1458,17 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B34" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B35" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
         <v>73</v>
       </c>
@@ -1440,52 +1476,55 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B38" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B39" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B40" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B41" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B42" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B43" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B44" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B45" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B46" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="F46" s="4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
         <v>81</v>
       </c>
@@ -1493,184 +1532,207 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B49" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B50" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B51" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B52" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B53" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B54" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B54" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B55" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B56" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" ht="15.6" x14ac:dyDescent="0.45">
+      <c r="F56" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.6" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B58" s="2" t="s">
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B59" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B59" s="2" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B60" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B60" s="2" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B61" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B61" s="2" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B62" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B62" s="2" t="s">
+      <c r="E62" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A64" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A64" s="2" t="s">
+      <c r="B64" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B64" s="2" t="s">
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B65" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B66" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B67" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B68" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A70" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B65" s="2" t="s">
+      <c r="B70" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B71" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B72" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B73" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B66" s="2" t="s">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B75" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B67" s="2" t="s">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B76" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B68" s="2" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B77" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A79" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A70" s="2" t="s">
+      <c r="B79" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B80" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B81" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B82" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F82" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A84" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B84" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B85" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B71" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B72" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B73" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B75" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B76" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B77" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A79" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B80" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B81" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B82" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A84" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B85" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B86" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B87" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B87" s="2" t="s">
-        <v>97</v>
+      <c r="E87" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="E88" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1680,6 +1742,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4f770298-b31c-4238-a90d-db1340869ae4">
@@ -1688,15 +1759,6 @@
     <TaxCatchAll xmlns="4ebca473-6c88-4eeb-9b46-7f2093239612" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1907,20 +1969,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68EEC494-2A78-4B3D-9A2E-CC561A7B8B93}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61D35B6F-58DC-4BFD-8311-2E7BC05345C9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="4f770298-b31c-4238-a90d-db1340869ae4"/>
     <ds:schemaRef ds:uri="4ebca473-6c88-4eeb-9b46-7f2093239612"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68EEC494-2A78-4B3D-9A2E-CC561A7B8B93}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
